--- a/feedback_forms/012_performance_review--feedback_forms.xlsx
+++ b/feedback_forms/012_performance_review--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'satisfactory'}</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Satisfactory'}</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsatisfactory'}</t>
+          <t>unsatisfactory</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Unsatisfactory'}</t>
+          <t>Unsatisfactory</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'semiannually'}</t>
+          <t>semiannually</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Semiannually'}</t>
+          <t>Semiannually</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'teamwork'}</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Teamwork'}</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Time Management'}</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'adaptability'}</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Adaptability'}</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1884,12 +1884,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2037,12 +2037,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2122,12 +2122,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2241,12 +2241,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2428,12 +2428,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
